--- a/submissions/GroupFormation/STA380GroupForm.xlsx
+++ b/submissions/GroupFormation/STA380GroupForm.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ginoli/Desktop/sta380/project/Shinny app/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ginoli/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743FC20A-F0E4-FD43-8E65-AF15861F1A84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0602ACEA-926B-3B45-83E9-FD24C3F02A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1860" yWindow="740" windowWidth="23560" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/submissions/GroupFormation/STA380GroupForm.xlsx
+++ b/submissions/GroupFormation/STA380GroupForm.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ginoli/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shenqianying/Desktop/Sta380 Project/submissions/GroupFormation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0602ACEA-926B-3B45-83E9-FD24C3F02A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D749E528-D259-374C-85B7-03C8F31B4837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1860" yWindow="740" windowWidth="23560" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -125,6 +125,18 @@
   </si>
   <si>
     <t>https://github.com/masinan123/STA380-Project.git</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianying Shen</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>shenqi18</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>qqianyingshen</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -596,6 +608,21 @@
       <c r="A23" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="B23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23">
+        <v>1008806393</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">

--- a/submissions/GroupFormation/STA380GroupForm.xlsx
+++ b/submissions/GroupFormation/STA380GroupForm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shenqianying/Desktop/Sta380 Project/submissions/GroupFormation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Documents\STA380-Project\submissions\GroupFormation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D749E528-D259-374C-85B7-03C8F31B4837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72CF3A9-01C7-4487-8DAC-FA7BB18A854A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="740" windowWidth="23560" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4245" yWindow="4410" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -138,13 +138,22 @@
   <si>
     <t>qqianyingshen</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kevin Luo</t>
+  </si>
+  <si>
+    <t>luoyu21</t>
+  </si>
+  <si>
+    <t>KevinYuChenLuo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -237,8 +246,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -455,17 +464,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.1640625" customWidth="1"/>
-    <col min="4" max="4" width="18.1640625" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="13.1640625" customWidth="1"/>
+    <col min="1" max="1" width="31.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -473,12 +482,12 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
         <v>2</v>
@@ -486,67 +495,67 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1">
       <c r="A18" s="3"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="3" t="s">
         <v>8</v>
@@ -564,7 +573,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>13</v>
       </c>
@@ -584,7 +593,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>15</v>
       </c>
@@ -604,7 +613,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>20</v>
       </c>
@@ -624,32 +633,47 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24">
+        <v>1008166100</v>
+      </c>
+      <c r="E24" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1">
       <c r="A27" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1">
       <c r="A28" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1">
       <c r="A29" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1">
       <c r="A30" s="5" t="s">
         <v>26</v>
       </c>
@@ -658,6 +682,7 @@
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="F21" r:id="rId1" xr:uid="{160CEE8E-A216-BA42-91E8-BA7CDE37079B}"/>
+    <hyperlink ref="F24" r:id="rId2" xr:uid="{A4FF2D33-40A0-4420-8059-6D6845E20ADE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/submissions/GroupFormation/STA380GroupForm.xlsx
+++ b/submissions/GroupFormation/STA380GroupForm.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Documents\STA380-Project\submissions\GroupFormation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\R_4.4.1\STA380 Project\submissions\GroupFormation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72CF3A9-01C7-4487-8DAC-FA7BB18A854A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A746A2-3606-4B10-98D8-60CD7F6EB561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4245" yWindow="4410" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="60">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -92,39 +92,36 @@
     <t>BarrelTitorrr</t>
   </si>
   <si>
+    <t>Student 3</t>
+  </si>
+  <si>
+    <t>Student 4</t>
+  </si>
+  <si>
+    <t>Student 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each group member is expected to contribute equally to the project. It is the responsibility of the group to allocate duties fairly, understanding that not everyone needs to be involved in every task. </t>
+  </si>
+  <si>
+    <t>For instance, it may not be feasible for all members to meet and collect data together.</t>
+  </si>
+  <si>
+    <t>All students within the same group will receive the same mark. However, your grade may be reduced if most of your group reports that you did not contribute or cooperate adequately.</t>
+  </si>
+  <si>
+    <t>To report an inactive member, please refer to the "Reporting Inactive Members" section under the project description.</t>
+  </si>
+  <si>
+    <t>liyiqia6</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gino968</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>https://github.com/masinan123/STA380-Project.git</t>
-  </si>
-  <si>
-    <t>Student 3</t>
-  </si>
-  <si>
-    <t>Student 4</t>
-  </si>
-  <si>
-    <t>Student 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each group member is expected to contribute equally to the project. It is the responsibility of the group to allocate duties fairly, understanding that not everyone needs to be involved in every task. </t>
-  </si>
-  <si>
-    <t>For instance, it may not be feasible for all members to meet and collect data together.</t>
-  </si>
-  <si>
-    <t>All students within the same group will receive the same mark. However, your grade may be reduced if most of your group reports that you did not contribute or cooperate adequately.</t>
-  </si>
-  <si>
-    <t>To report an inactive member, please refer to the "Reporting Inactive Members" section under the project description.</t>
-  </si>
-  <si>
-    <t>liyiqia6</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gino968</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://github.com/masinan123/STA380-Project.git</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -147,13 +144,108 @@
   </si>
   <si>
     <t>KevinYuChenLuo</t>
+  </si>
+  <si>
+    <t>Sinan Ma</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>masinan</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>masinan123</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Permutation Test for Two-Sample Comparison</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Not applicable. A real dataset from a published research article with two distinct groups will be used.</t>
+  </si>
+  <si>
+    <t>We select a dataset from a published study containing two independent groups suitable for a two-sample comparison.</t>
+  </si>
+  <si>
+    <t>A permutation test will be performed using a chosen test statistic.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>The permutation distribution will be generated, and the p-value will be computed and reported.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Shiny app will visualizes the permutation distribution and states whether the null hypothesis is rejected or not.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bootstrap Confidence Intervals and Coverage Probability</t>
+  </si>
+  <si>
+    <t>Simulated data generated from distributions with known parameters, including symmetric and skewed distributions.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>We will use bootstrap resampling to construct confidence intervals for population parameters.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Using Monte Carlo simulation, we will study the empirical coverage probability of bootstrap confidence intervals under different sample sizes.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Shiny app wil be displaying bootstrap distributions, confidence intervals, and estimated coverage rates to illustrate the finite-sample behavior of bootstrap methods.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inverse-Transform Sampling and Numerical Accuracy</t>
+  </si>
+  <si>
+    <t>Distributions with known cumulative distribution functions, including cases where the inverse CDF is available in closed form and cases requiring numerical inversion.</t>
+  </si>
+  <si>
+    <t>We will implement the inverse-transform method to generate random variables from specified distributions.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>The project will show how numerical approximation of the inverse CDF affects sampling accuracy, especially in tail regions.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Shiny app will be comparing simulated distributions with theoretical densities and highlights numerical errors in inverse-transform sampling.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/KevinYuChenLuo</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/masinan123</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/qqianyingshen</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/Gino968</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/BarrelTitorrr</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Group Github Rep Link</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -463,8 +555,8 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.7109375" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
@@ -474,7 +566,7 @@
     <col min="6" max="6" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -482,12 +574,12 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
         <v>2</v>
@@ -495,194 +587,296 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1">
+      <c r="B5" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1">
+      <c r="B6" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1">
+      <c r="B7" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1">
+      <c r="B8" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A10" s="3" t="s">
+      <c r="B9" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3"/>
+      <c r="B10" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3"/>
+      <c r="B11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A11" s="3" t="s">
+      <c r="B12" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A12" s="3" t="s">
+      <c r="B13" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A14" s="3"/>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A15" s="3" t="s">
+      <c r="B14" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="3"/>
+      <c r="B15" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="3"/>
+      <c r="B16" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3"/>
+      <c r="B17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A16" s="3" t="s">
+      <c r="B18" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A17" s="3" t="s">
+      <c r="B19" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A18" s="3"/>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A20" s="1"/>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="3"/>
+      <c r="B21" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1"/>
+      <c r="B24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A21" s="3" t="s">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B25" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25">
+        <v>1010463008</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D21">
-        <v>1010463008</v>
-      </c>
-      <c r="E21" s="4" t="s">
+      <c r="F25" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26">
+        <v>1009969795</v>
+      </c>
+      <c r="E26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27">
+        <v>1008806393</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28">
+        <v>1008166100</v>
+      </c>
+      <c r="E28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29">
+        <v>1007673322</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="3"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22">
-        <v>1009969795</v>
-      </c>
-      <c r="E22" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23">
-        <v>1008806393</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24">
-        <v>1008166100</v>
-      </c>
-      <c r="E24" t="s">
-        <v>35</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A25" s="3" t="s">
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="3"/>
+      <c r="B32" s="6"/>
+    </row>
+    <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A27" s="5" t="s">
+    <row r="34" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A28" s="5" t="s">
+    <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A29" s="5" t="s">
+    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A30" s="5" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F21" r:id="rId1" xr:uid="{160CEE8E-A216-BA42-91E8-BA7CDE37079B}"/>
-    <hyperlink ref="F24" r:id="rId2" xr:uid="{A4FF2D33-40A0-4420-8059-6D6845E20ADE}"/>
+    <hyperlink ref="F25" r:id="rId1" xr:uid="{160CEE8E-A216-BA42-91E8-BA7CDE37079B}"/>
+    <hyperlink ref="F28" r:id="rId2" xr:uid="{A4FF2D33-40A0-4420-8059-6D6845E20ADE}"/>
+    <hyperlink ref="F29" r:id="rId3" xr:uid="{FE082C7C-AC32-4344-851C-9F7CF8B2CBBF}"/>
+    <hyperlink ref="F27" r:id="rId4" xr:uid="{AA78BE49-6391-481A-B562-B69089110561}"/>
+    <hyperlink ref="F26" r:id="rId5" xr:uid="{718A4352-9A60-4B3C-9673-7FA4759272C8}"/>
+    <hyperlink ref="B31" r:id="rId6" xr:uid="{700D4A9F-0D0F-49DF-A571-F183A6E3A027}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/submissions/GroupFormation/STA380GroupForm.xlsx
+++ b/submissions/GroupFormation/STA380GroupForm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\R_4.4.1\STA380 Project\submissions\GroupFormation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A746A2-3606-4B10-98D8-60CD7F6EB561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADFBA451-9348-46BD-B8A9-56B319EC3140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -158,86 +158,90 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Permutation Test for Two-Sample Comparison</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Not applicable. A real dataset from a published research article with two distinct groups will be used.</t>
-  </si>
-  <si>
-    <t>We select a dataset from a published study containing two independent groups suitable for a two-sample comparison.</t>
-  </si>
-  <si>
-    <t>A permutation test will be performed using a chosen test statistic.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>The permutation distribution will be generated, and the p-value will be computed and reported.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>The Shiny app will visualizes the permutation distribution and states whether the null hypothesis is rejected or not.</t>
+    <t>Simulated data generated from distributions with known parameters, including symmetric and skewed distributions.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inverse-Transform Sampling and Numerical Accuracy</t>
+  </si>
+  <si>
+    <t>https://github.com/KevinYuChenLuo</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/masinan123</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/qqianyingshen</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/Gino968</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/BarrelTitorrr</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Group Github Rep Link</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">We will use the World Population Prospects 2024 dataset published by the United Nations DESA. </t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>A permutation test will be performed to determine if the difference in mean growth rates between these two groups is statistically significant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We will subset the data to compare the mean Population Growth Rate (percentage) between two distinct development groups: </t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">"More developed regions" and "Less developed regions". </t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Bootstrap Confidence Intervals and Coverage Probability</t>
-  </si>
-  <si>
-    <t>Simulated data generated from distributions with known parameters, including symmetric and skewed distributions.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>We will use bootstrap resampling to construct confidence intervals for population parameters.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Using Monte Carlo simulation, we will study the empirical coverage probability of bootstrap confidence intervals under different sample sizes.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>The Shiny app wil be displaying bootstrap distributions, confidence intervals, and estimated coverage rates to illustrate the finite-sample behavior of bootstrap methods.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Inverse-Transform Sampling and Numerical Accuracy</t>
-  </si>
-  <si>
-    <t>Distributions with known cumulative distribution functions, including cases where the inverse CDF is available in closed form and cases requiring numerical inversion.</t>
-  </si>
-  <si>
-    <t>We will implement the inverse-transform method to generate random variables from specified distributions.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>The project will show how numerical approximation of the inverse CDF affects sampling accuracy, especially in tail regions.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>The Shiny app will be comparing simulated distributions with theoretical densities and highlights numerical errors in inverse-transform sampling.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://github.com/KevinYuChenLuo</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://github.com/masinan123</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://github.com/qqianyingshen</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://github.com/Gino968</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://github.com/BarrelTitorrr</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Group Github Rep Link</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Extra details:</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">We will use the Global analysis of environmental and socioeconomic factors associated with human burden of environmentally mediated pathogens dataset from </t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dryad, which contains continuous variables such as country-level disease burden measures.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bootstrap resampling will be applied to estimate confidence intervals for a chosen continuous variable (e.g., mean or median disease burden).</t>
+  </si>
+  <si>
+    <t>The Shiny app will display bootstrap distributions, confidence intervals, and analysis of interval width and stability.</t>
+  </si>
+  <si>
+    <t>Exponential distribution with rate parameter lambda, and Weibull distribution with shape parameter k and scale parameter lambda.</t>
+  </si>
+  <si>
+    <t>We will implement the inverse-transform method to generate random variables from the Exponential(lambda) and Weibull(k, lambda) distributions.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>For each distribution, the inverse CDF will be derived explicitly and used to transform Uniform(0,1) random variables.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Simulated samples will be compared with the corresponding theoretical density functions using histograms and density plots in the Shiny app.</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -555,7 +559,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.7109375" customWidth="1"/>
@@ -592,7 +596,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -600,7 +604,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -608,275 +612,263 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
       <c r="B9" s="4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
+      <c r="A10" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="B10" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="3"/>
-      <c r="B11" s="4"/>
+      <c r="A11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>4</v>
-      </c>
+      <c r="A13" s="3"/>
       <c r="B13" s="4" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="A14" s="3"/>
       <c r="B14" s="4" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
       <c r="B15" s="4" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="3"/>
+      <c r="A16" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="B16" s="4" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="3"/>
-      <c r="B17" s="4"/>
+      <c r="A17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="B19" s="4" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="B20" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="3"/>
-      <c r="B21" s="4" t="s">
-        <v>52</v>
+      <c r="A21" s="1"/>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="B22" s="4" t="s">
-        <v>53</v>
+        <v>14</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22">
+        <v>1010463008</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="4"/>
+      <c r="A23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23">
+        <v>1009969795</v>
+      </c>
+      <c r="E23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
-      <c r="B24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>12</v>
+      <c r="A24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24">
+        <v>1008806393</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
       </c>
       <c r="D25">
-        <v>1010463008</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>27</v>
+        <v>1008166100</v>
+      </c>
+      <c r="E25" t="s">
+        <v>34</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D26">
-        <v>1009969795</v>
-      </c>
-      <c r="E26" t="s">
-        <v>18</v>
+        <v>1007673322</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27">
-        <v>1008806393</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>56</v>
-      </c>
+      <c r="A27" s="3"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="6"/>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28">
-        <v>1008166100</v>
-      </c>
-      <c r="E28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>54</v>
+        <v>45</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D29">
-        <v>1007673322</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>55</v>
-      </c>
+      <c r="A29" s="3"/>
+      <c r="B29" s="6"/>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="3"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="6"/>
+      <c r="A30" s="5" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>28</v>
+      <c r="A31" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="3"/>
-      <c r="B32" s="6"/>
+      <c r="A32" s="5" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="5" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F25" r:id="rId1" xr:uid="{160CEE8E-A216-BA42-91E8-BA7CDE37079B}"/>
-    <hyperlink ref="F28" r:id="rId2" xr:uid="{A4FF2D33-40A0-4420-8059-6D6845E20ADE}"/>
-    <hyperlink ref="F29" r:id="rId3" xr:uid="{FE082C7C-AC32-4344-851C-9F7CF8B2CBBF}"/>
-    <hyperlink ref="F27" r:id="rId4" xr:uid="{AA78BE49-6391-481A-B562-B69089110561}"/>
-    <hyperlink ref="F26" r:id="rId5" xr:uid="{718A4352-9A60-4B3C-9673-7FA4759272C8}"/>
-    <hyperlink ref="B31" r:id="rId6" xr:uid="{700D4A9F-0D0F-49DF-A571-F183A6E3A027}"/>
+    <hyperlink ref="F22" r:id="rId1" xr:uid="{160CEE8E-A216-BA42-91E8-BA7CDE37079B}"/>
+    <hyperlink ref="F25" r:id="rId2" xr:uid="{A4FF2D33-40A0-4420-8059-6D6845E20ADE}"/>
+    <hyperlink ref="F26" r:id="rId3" xr:uid="{FE082C7C-AC32-4344-851C-9F7CF8B2CBBF}"/>
+    <hyperlink ref="F24" r:id="rId4" xr:uid="{AA78BE49-6391-481A-B562-B69089110561}"/>
+    <hyperlink ref="F23" r:id="rId5" xr:uid="{718A4352-9A60-4B3C-9673-7FA4759272C8}"/>
+    <hyperlink ref="B28" r:id="rId6" xr:uid="{700D4A9F-0D0F-49DF-A571-F183A6E3A027}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
